--- a/job_application_forms/042_south_jersey_babysitter_application_form--job_application_forms.xlsx
+++ b/job_application_forms/042_south_jersey_babysitter_application_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>application_form</t>
+          <t>applicant_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Application Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter your full name.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>availability</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please indicate your days available to work.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>experience</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe your previous work experience.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -594,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>education</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>List your degrees earned.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,23 +623,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>references</t>
+          <t>special_skills</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>references</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Special Skills</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Check all that apply.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>special_skills</t>
+          <t>certifications</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>special_skills</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Certifications</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>List your certifications.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>availability_details</t>
+          <t>earliest_start_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>availability_details</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Earliest Start Date</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter the earliest date you are available to start.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>availability</t>
+          <t>latest_end_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>availability</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Latest End Date</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please enter the latest date you are available to work.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>earliest_start_date</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>earliest_start_date</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Emergency Contact</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please enter emergency contact information.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>latest_end_date</t>
+          <t>emergency_contact_relationship</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>latest_end_date</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Emergency Contact Relationship</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Describe your relationship to emergency contact.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>earliest_start_time</t>
+          <t>emergency_contact_phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>earliest_start_time</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Emergency Contact Phone</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please enter emergency contact phone number.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>latest_end_time</t>
+          <t>emergency_contact_email</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>latest_end_time</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Emergency Contact Email</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please enter emergency contact email.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,18 +844,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>emergency_contact</t>
+          <t>emergency_contact_relationship_other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>emergency_contact</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Emergency Contact Relationship Other</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Describe your relationship to emergency contact.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,18 +871,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship</t>
+          <t>emergency_contact_relationship_other_phone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Emergency Contact Relationship Other Phone</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please enter emergency contact phone number.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -842,246 +898,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>emergency_contact_phone</t>
+          <t>emergency_contact_relationship_other_email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>emergency_contact_phone</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Emergency Contact Relationship Other Email</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please enter emergency contact email.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_job</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_job</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_phone</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_phone</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_email</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_phone</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_phone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_email</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_email</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_phone</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_phone</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_email</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_email</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_phone</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_phone</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +928,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1245,15 +1075,66 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>availability_choices</t>
+          <t>special_skills_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>cpr_certification</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CPR Certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>special_skills_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>first_aid_certification</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>First Aid Certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>special_skills_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>swimming_lessons</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Swimming Lessons</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>special_skills_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>other_(please_specify)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Other (Please specify)</t>
         </is>
